--- a/data/axe1/ALTERMAP_2026_Vision_du_Monde_SMA_labels.xlsx
+++ b/data/axe1/ALTERMAP_2026_Vision_du_Monde_SMA_labels.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/claudegrasland1/Documents/cg/projet/_ALTERMAP/axes/axe1-worldmap/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/claudegrasland1/worldregio/altermap/data/axe1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{168E2BE4-EA1B-7940-8ECF-82CC334F015E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A5A685-AF68-4143-83EA-BB692306E244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="760" windowWidth="32180" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3801" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3801" uniqueCount="1066">
   <si>
     <t>start</t>
   </si>
@@ -3215,6 +3215,9 @@
   </si>
   <si>
     <t>uuid:7948b4e9-cb27-4018-92df-404fa0698422</t>
+  </si>
+  <si>
+    <t>024</t>
   </si>
 </sst>
 </file>
@@ -3253,9 +3256,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9264,8 +9268,8 @@
       <c r="D25" t="s">
         <v>476</v>
       </c>
-      <c r="E25" t="s">
-        <v>592</v>
+      <c r="E25" s="2" t="s">
+        <v>1065</v>
       </c>
       <c r="F25" s="1">
         <v>46104</v>
